--- a/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>Property</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Value Set (all codes)</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r372-type-groupe-gco?vs</t>
+  </si>
+  <si>
     <t>Hierarchy</t>
   </si>
   <si>
@@ -146,6 +149,36 @@
   </si>
   <si>
     <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>Statut d'un code concept</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date de dépréciation du code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date de retrait du code</t>
   </si>
   <si>
     <t>Level</t>
@@ -434,46 +467,48 @@
       <c r="A15" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -483,57 +518,99 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>20</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -548,63 +625,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2"/>
     </row>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
@@ -157,7 +157,7 @@
     <t>http://hl7.org/fhir/concept-properties#status</t>
   </si>
   <si>
-    <t>Statut d'un code concept</t>
+    <t>A code that indicates the status of the concept. Typical values are active, experimental, deprecated, and retired</t>
   </si>
   <si>
     <t>code</t>
@@ -169,7 +169,7 @@
     <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
   </si>
   <si>
-    <t>Date de dépréciation du code</t>
+    <t>The date at which a concept was deprecated. Concepts that are deprecated but not inactive can still be used, but their use is discouraged, and they should be expected to be made inactive in a future release. Property type is dateTime. Note that the status property may also be used to indicate that a concept is deprecated</t>
   </si>
   <si>
     <t>retirementDate</t>
@@ -178,7 +178,7 @@
     <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
   </si>
   <si>
-    <t>Date de retrait du code</t>
+    <t>The date at which a concept was retired</t>
   </si>
   <si>
     <t>Level</t>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="70">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241230120000</t>
+    <t>202507110000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T12:00:00+01:00</t>
+    <t>2025-07-11T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,9 +94,6 @@
     <t>Value Set (all codes)</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r372-type-groupe-gco?vs</t>
-  </si>
-  <si>
     <t>Hierarchy</t>
   </si>
   <si>
@@ -179,6 +176,18 @@
   </si>
   <si>
     <t>The date at which a concept was retired</t>
+  </si>
+  <si>
+    <t>finess</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#finess</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts utilisés par FINESS+</t>
+  </si>
+  <si>
+    <t>boolean</t>
   </si>
   <si>
     <t>Level</t>
@@ -467,48 +476,46 @@
       <c r="A15" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -518,99 +525,113 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>35</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>20</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B5" t="s" s="2">
+      <c r="C5" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="C5" t="s" s="2">
+      <c r="D5" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="B6" t="s" s="2">
+      <c r="C6" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="C6" t="s" s="2">
-        <v>51</v>
-      </c>
       <c r="D6" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="C7" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="C7" t="s" s="2">
+      <c r="D7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>40</v>
+      <c r="B8" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -625,63 +646,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D5" s="2"/>
     </row>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
@@ -181,7 +181,7 @@
     <t>finess</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/concept-properties#finess</t>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#finess</t>
   </si>
   <si>
     <t>Permet de définir les codes concepts utilisés par FINESS+</t>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -130,6 +130,9 @@
     <t>dateValid</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
     <t>date de validité d'un code concept</t>
   </si>
   <si>
@@ -139,10 +142,16 @@
     <t>dateMaj</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
     <t>Date de mise à jour d'un code concept</t>
   </si>
   <si>
     <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
   </si>
   <si>
     <t>Date de fin d'exploitation d'un code concept</t>
@@ -546,92 +555,98 @@
       <c r="A2" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="C2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>45</v>
+      </c>
       <c r="C4" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -646,63 +661,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>34</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2"/>
     </row>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202507110000</t>
+    <t>20250711120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250711120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-11T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r372-type-groupe-gco.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="75">
   <si>
     <t>Property</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -366,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -465,66 +471,74 @@
       <c r="A12" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B19" t="s" s="2">
         <v>30</v>
       </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B20" s="2"/>
+      <c r="B20" t="s" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s" s="2">
         <v>33</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -539,114 +553,114 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -661,63 +675,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D5" s="2"/>
     </row>
